--- a/data/output/manager_summary.xlsx
+++ b/data/output/manager_summary.xlsx
@@ -420,19 +420,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>34219570.14</v>
+        <v>73104060.8926</v>
       </c>
       <c r="D2">
-        <v>32371096.8</v>
+        <v>67429987.90000001</v>
       </c>
       <c r="E2">
-        <v>-2097612.33</v>
+        <v>-6328581.4</v>
       </c>
       <c r="F2">
-        <v>517639.77</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/manager_summary.xlsx
+++ b/data/output/manager_summary.xlsx
@@ -423,13 +423,13 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>73104060.8926</v>
+        <v>72887640.49259999</v>
       </c>
       <c r="D2">
-        <v>67429987.90000001</v>
+        <v>67380038.09999999</v>
       </c>
       <c r="E2">
-        <v>-6328581.4</v>
+        <v>-6149429.500000001</v>
       </c>
       <c r="F2">
         <v>0</v>
